--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\测试\auto_framework\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\测试\webui_kdt_framework\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="9840" windowHeight="4560"/>
+    <workbookView windowWidth="17865" windowHeight="6060"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,57 +34,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>编号</t>
   </si>
   <si>
-    <t>模块</t>
-  </si>
-  <si>
-    <t>场景</t>
-  </si>
-  <si>
-    <t>标题</t>
-  </si>
-  <si>
-    <t>请求方式</t>
-  </si>
-  <si>
-    <t>路径</t>
-  </si>
-  <si>
-    <t>请求头</t>
-  </si>
-  <si>
-    <t>url参数</t>
-  </si>
-  <si>
-    <t>data参数</t>
-  </si>
-  <si>
-    <t>json参数</t>
-  </si>
-  <si>
-    <t>文件参数</t>
-  </si>
-  <si>
-    <t>校验字段</t>
-  </si>
-  <si>
-    <t>预期结果</t>
-  </si>
-  <si>
-    <t>数据库校验内容</t>
-  </si>
-  <si>
-    <t>数据库预期结果</t>
-  </si>
-  <si>
-    <t>json提取</t>
-  </si>
-  <si>
-    <t>sql提取</t>
+    <t>步骤序号</t>
+  </si>
+  <si>
+    <t>步骤名称</t>
   </si>
   <si>
     <t>是否执行</t>
@@ -93,169 +51,31 @@
     <t>id</t>
   </si>
   <si>
-    <t>feature</t>
-  </si>
-  <si>
-    <t>story</t>
-  </si>
-  <si>
-    <t>title</t>
-  </si>
-  <si>
-    <t>method</t>
-  </si>
-  <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>headers</t>
-  </si>
-  <si>
-    <t>params</t>
-  </si>
-  <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>json</t>
-  </si>
-  <si>
-    <t>files</t>
-  </si>
-  <si>
-    <t>check</t>
-  </si>
-  <si>
-    <t>expected</t>
-  </si>
-  <si>
-    <t>sql_check</t>
-  </si>
-  <si>
-    <t>sql_expected</t>
-  </si>
-  <si>
-    <t>jsonExData</t>
-  </si>
-  <si>
-    <t>sqlExData</t>
+    <t>step_num</t>
+  </si>
+  <si>
+    <t>step_name</t>
   </si>
   <si>
     <t>is_true</t>
   </si>
   <si>
-    <t>登录</t>
-  </si>
-  <si>
-    <t>登陆成功</t>
-  </si>
-  <si>
-    <t>管理员登陆成功</t>
-  </si>
-  <si>
-    <t>post</t>
-  </si>
-  <si>
-    <t>/login</t>
-  </si>
-  <si>
-    <t>{"username":"admin","password":"123456"}</t>
-  </si>
-  <si>
-    <t>$..msg</t>
-  </si>
-  <si>
-    <t>登录成功</t>
-  </si>
-  <si>
-    <t>select mg_name from sp_manager where mg_name="admin"</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
-    <t>{"TOKEN":"$..token"}</t>
-  </si>
-  <si>
-    <t>{"ADMIN_NAME":"select mg_name from sp_manager where mg_name='admin'"}</t>
-  </si>
-  <si>
-    <t>用户管理</t>
-  </si>
-  <si>
-    <t>查询失败</t>
-  </si>
-  <si>
-    <t>未登录状态，查询用户列表失败</t>
-  </si>
-  <si>
-    <t>get</t>
-  </si>
-  <si>
-    <t>/users</t>
-  </si>
-  <si>
-    <t>{"pagenum":1,"pagesize":1}</t>
-  </si>
-  <si>
-    <t>无效token</t>
-  </si>
-  <si>
-    <t>查询成功</t>
-  </si>
-  <si>
-    <t>查询用户数据列表成功</t>
-  </si>
-  <si>
-    <t>{"Authorization":"{{TOKEN}}"}</t>
-  </si>
-  <si>
-    <t>获取管理员列表成功</t>
-  </si>
-  <si>
-    <t>新增成功</t>
-  </si>
-  <si>
-    <t>添加一个用户，添加成功</t>
-  </si>
-  <si>
-    <t>{"username":"meiqi","password":"123456"}</t>
-  </si>
-  <si>
-    <t>创建成功</t>
-  </si>
-  <si>
-    <t>{"MEIQI_ID":"$..id"}</t>
-  </si>
-  <si>
-    <t>修改成功</t>
-  </si>
-  <si>
-    <t>修改用户状态，修改成功</t>
-  </si>
-  <si>
-    <t>put</t>
-  </si>
-  <si>
-    <t>/users/{{MEIQI_ID}}/state/true</t>
-  </si>
-  <si>
-    <t>设置状态成功</t>
-  </si>
-  <si>
-    <t>图片上传</t>
-  </si>
-  <si>
-    <t>上传成功</t>
-  </si>
-  <si>
-    <t>图片上传成功</t>
-  </si>
-  <si>
-    <t>/upload</t>
-  </si>
-  <si>
-    <t>{"file":("1.jpg",open("./file/1.jpg","rb"),"jpg")}</t>
+    <t>case1</t>
+  </si>
+  <si>
+    <t>case1-1</t>
+  </si>
+  <si>
+    <t>case1-2</t>
+  </si>
+  <si>
+    <t>case2</t>
+  </si>
+  <si>
+    <t>case2-1</t>
+  </si>
+  <si>
+    <t>case2-2</t>
   </si>
 </sst>
 </file>
@@ -623,7 +443,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -641,6 +461,32 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -770,7 +616,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -782,34 +628,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
@@ -894,18 +740,33 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1218,25 +1079,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
-    <col min="3" max="3" width="8.875" customWidth="1"/>
-    <col min="4" max="4" width="29.625" customWidth="1"/>
-    <col min="6" max="6" width="33.75" customWidth="1"/>
-    <col min="7" max="7" width="32.625" customWidth="1"/>
-    <col min="8" max="8" width="28.25" customWidth="1"/>
-    <col min="9" max="9" width="44.875" customWidth="1"/>
-    <col min="11" max="11" width="53.75" customWidth="1"/>
-    <col min="12" max="12" width="9.375" customWidth="1"/>
-    <col min="13" max="13" width="19.125" customWidth="1"/>
-    <col min="14" max="14" width="58.25" customWidth="1"/>
-    <col min="15" max="15" width="15" customWidth="1"/>
-    <col min="16" max="16" width="22.625" customWidth="1"/>
-    <col min="17" max="17" width="77.125" customWidth="1"/>
+    <col min="1" max="1" width="5.375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1249,315 +1101,76 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:4">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+    </row>
+    <row r="3" s="2" customFormat="1" spans="1:4">
+      <c r="A3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="D3" s="4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" s="2" customFormat="1" spans="1:4">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5">
+        <v>2</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="D4" s="6"/>
+    </row>
+    <row r="5" s="2" customFormat="1" spans="1:4">
+      <c r="A5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="D5" s="7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" s="2" customFormat="1" spans="1:4">
+      <c r="A6" s="8"/>
+      <c r="B6" s="5">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:18">
-      <c r="A2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q2" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" spans="1:18">
-      <c r="A3" s="2">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="R3" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" s="2" customFormat="1" spans="1:18">
-      <c r="A4" s="2">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="R4" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" s="2" customFormat="1" spans="1:18">
-      <c r="A5" s="2">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="R5" s="2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" s="2" customFormat="1" spans="1:18">
-      <c r="A6" s="2">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:18">
-      <c r="A7" s="2">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="L7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:18">
-      <c r="A8" s="2">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="R8" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="D6" s="8"/>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="17865" windowHeight="6060"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>编号</t>
   </si>
@@ -76,6 +76,24 @@
   </si>
   <si>
     <t>case2-2</t>
+  </si>
+  <si>
+    <t>case3</t>
+  </si>
+  <si>
+    <t>case3-1</t>
+  </si>
+  <si>
+    <t>case3-2</t>
+  </si>
+  <si>
+    <t>case4</t>
+  </si>
+  <si>
+    <t>case4-1</t>
+  </si>
+  <si>
+    <t>case4-2</t>
   </si>
 </sst>
 </file>
@@ -744,28 +762,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1082,87 +1100,87 @@
   <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="2" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11.625" style="2" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="5.375" style="8" customWidth="1"/>
+    <col min="2" max="2" width="10.375" style="8" customWidth="1"/>
+    <col min="3" max="3" width="11.625" style="8" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:4">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="7" customFormat="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:4">
-      <c r="A2" s="3" t="s">
+    <row r="2" s="7" customFormat="1" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:4">
-      <c r="A3" s="4" t="s">
+    <row r="3" s="8" customFormat="1" spans="1:4">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="4" t="b">
+      <c r="D3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:4">
-      <c r="A4" s="6"/>
-      <c r="B4" s="5">
+    <row r="4" s="8" customFormat="1" spans="1:4">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6"/>
+      <c r="D4" s="4"/>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:4">
-      <c r="A5" s="7" t="s">
+    <row r="5" s="8" customFormat="1" spans="1:4">
+      <c r="A5" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="3">
         <v>1</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="7" t="b">
+      <c r="D5" s="5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:4">
-      <c r="A6" s="8"/>
-      <c r="B6" s="5">
+    <row r="6" s="8" customFormat="1" spans="1:4">
+      <c r="A6" s="6"/>
+      <c r="B6" s="3">
         <v>2</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="8"/>
+      <c r="D6" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1180,9 +1198,92 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3">
+        <v>2</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="3">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255" activeTab="1"/>
+    <workbookView windowWidth="16140" windowHeight="5910" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,66 +34,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
   <si>
     <t>编号</t>
   </si>
   <si>
+    <t>模块</t>
+  </si>
+  <si>
+    <t>场景</t>
+  </si>
+  <si>
+    <t>标题</t>
+  </si>
+  <si>
     <t>步骤序号</t>
   </si>
   <si>
     <t>步骤名称</t>
   </si>
   <si>
+    <t>关键动作</t>
+  </si>
+  <si>
+    <t>定位方式</t>
+  </si>
+  <si>
+    <t>元素信息</t>
+  </si>
+  <si>
+    <t>数据</t>
+  </si>
+  <si>
+    <t>组元素索引</t>
+  </si>
+  <si>
     <t>是否执行</t>
   </si>
   <si>
     <t>id</t>
   </si>
   <si>
+    <t>feature</t>
+  </si>
+  <si>
+    <t>story</t>
+  </si>
+  <si>
+    <t>title</t>
+  </si>
+  <si>
     <t>step_num</t>
   </si>
   <si>
     <t>step_name</t>
   </si>
   <si>
+    <t>keyword</t>
+  </si>
+  <si>
+    <t>by</t>
+  </si>
+  <si>
+    <t>value</t>
+  </si>
+  <si>
+    <t>data</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
     <t>is_true</t>
   </si>
   <si>
-    <t>case1</t>
-  </si>
-  <si>
-    <t>case1-1</t>
-  </si>
-  <si>
-    <t>case1-2</t>
-  </si>
-  <si>
-    <t>case2</t>
-  </si>
-  <si>
-    <t>case2-1</t>
-  </si>
-  <si>
-    <t>case2-2</t>
-  </si>
-  <si>
-    <t>case3</t>
-  </si>
-  <si>
-    <t>case3-1</t>
-  </si>
-  <si>
-    <t>case3-2</t>
-  </si>
-  <si>
-    <t>case4</t>
-  </si>
-  <si>
-    <t>case4-1</t>
-  </si>
-  <si>
-    <t>case4-2</t>
+    <t>login_1</t>
+  </si>
+  <si>
+    <t>登录</t>
+  </si>
+  <si>
+    <t>登录成功</t>
+  </si>
+  <si>
+    <t>账密正确，登陆成功</t>
+  </si>
+  <si>
+    <t>输入用户名</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>xpath</t>
+  </si>
+  <si>
+    <t>//input</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>输入密码</t>
+  </si>
+  <si>
+    <t>login_2</t>
+  </si>
+  <si>
+    <t>登录2</t>
   </si>
 </sst>
 </file>
@@ -461,7 +509,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -479,32 +527,6 @@
       <top style="thin">
         <color auto="1"/>
       </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -634,7 +656,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -646,34 +668,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
@@ -758,26 +780,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1097,16 +1110,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="5.375" style="8" customWidth="1"/>
-    <col min="2" max="2" width="10.375" style="8" customWidth="1"/>
-    <col min="3" max="3" width="11.625" style="8" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="8.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" style="5" customWidth="1"/>
+    <col min="3" max="3" width="8.875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="19.125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="10.375" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11.625" style="5" customWidth="1"/>
+    <col min="7" max="7" width="9.375" style="5" customWidth="1"/>
+    <col min="8" max="8" width="10.375" style="5" customWidth="1"/>
+    <col min="9" max="11" width="11.625" style="5" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="7" customFormat="1" spans="1:4">
+    <row r="1" s="4" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1119,75 +1138,136 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" s="7" customFormat="1" spans="1:4">
+    <row r="2" s="4" customFormat="1" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" s="8" customFormat="1" spans="1:4">
+    <row r="3" s="5" customFormat="1" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="3">
+        <v>24</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="b">
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" s="8" customFormat="1" spans="1:4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="3">
+    <row r="4" s="5" customFormat="1" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" s="8" customFormat="1" spans="1:4">
-      <c r="A5" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" s="8" customFormat="1" spans="1:4">
-      <c r="A6" s="6"/>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="6"/>
+      <c r="F4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="K4" s="3"/>
+      <c r="L4" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1198,10 +1278,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <cols>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="8.875" customWidth="1"/>
+    <col min="4" max="4" width="19.125" customWidth="1"/>
+    <col min="5" max="5" width="10.375" customWidth="1"/>
+    <col min="6" max="6" width="11.625" customWidth="1"/>
+    <col min="7" max="7" width="9.375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1214,75 +1302,138 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" s="3">
+        <v>34</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="2" t="b">
+      <c r="F3" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="4"/>
-      <c r="B4" s="3">
+    <row r="4" spans="1:12">
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="3">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="4"/>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="6"/>
+      <c r="F4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3">
+        <v>123456</v>
+      </c>
+      <c r="K4" s="3"/>
+      <c r="L4" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
     <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="L3:L4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="16140" windowHeight="5910" activeTab="1"/>
+    <workbookView windowWidth="15345" windowHeight="7335"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
   <si>
     <t>编号</t>
   </si>
@@ -108,10 +108,52 @@
     <t>is_true</t>
   </si>
   <si>
-    <t>login_1</t>
-  </si>
-  <si>
-    <t>登录</t>
+    <t>test_1</t>
+  </si>
+  <si>
+    <t>test</t>
+  </si>
+  <si>
+    <t>XX</t>
+  </si>
+  <si>
+    <t>XXX</t>
+  </si>
+  <si>
+    <t>打开网址</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>file:///E:/%E6%B5%8B%E8%AF%95/pagetest/pagetest/%E6%B3%A8%E5%86%8CA.html</t>
+  </si>
+  <si>
+    <t>输入用户名</t>
+  </si>
+  <si>
+    <t>input</t>
+  </si>
+  <si>
+    <t>xpath</t>
+  </si>
+  <si>
+    <t>//input</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>等待</t>
+  </si>
+  <si>
+    <t>wait</t>
+  </si>
+  <si>
+    <t>login_2</t>
+  </si>
+  <si>
+    <t>登录2</t>
   </si>
   <si>
     <t>登录成功</t>
@@ -120,28 +162,7 @@
     <t>账密正确，登陆成功</t>
   </si>
   <si>
-    <t>输入用户名</t>
-  </si>
-  <si>
-    <t>input</t>
-  </si>
-  <si>
-    <t>xpath</t>
-  </si>
-  <si>
-    <t>//input</t>
-  </si>
-  <si>
-    <t>admin</t>
-  </si>
-  <si>
     <t>输入密码</t>
-  </si>
-  <si>
-    <t>login_2</t>
-  </si>
-  <si>
-    <t>登录2</t>
   </si>
 </sst>
 </file>
@@ -509,7 +530,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -527,6 +548,43 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -656,7 +714,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -668,34 +726,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="10">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="12">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
@@ -780,7 +838,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -798,6 +856,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1110,8 +1180,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3"/>
+  <dimension ref="A1:L5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
   <cols>
     <col min="1" max="1" width="8.375" style="5" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="5" customWidth="1"/>
@@ -1121,7 +1191,9 @@
     <col min="6" max="6" width="11.625" style="5" customWidth="1"/>
     <col min="7" max="7" width="9.375" style="5" customWidth="1"/>
     <col min="8" max="8" width="10.375" style="5" customWidth="1"/>
-    <col min="9" max="11" width="11.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="11.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="80.375" style="5" customWidth="1"/>
+    <col min="11" max="11" width="11.625" style="5" customWidth="1"/>
     <col min="12" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
@@ -1202,16 +1274,16 @@
       </c>
     </row>
     <row r="3" s="5" customFormat="1" spans="1:12">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
         <v>27</v>
       </c>
       <c r="E3" s="3">
@@ -1223,51 +1295,71 @@
       <c r="G3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="2" t="b">
+      <c r="K3" s="3"/>
+      <c r="L3" s="6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4" s="5" customFormat="1" spans="1:12">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
       <c r="E4" s="3">
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>35</v>
+      </c>
       <c r="K4" s="3"/>
-      <c r="L4" s="2"/>
+      <c r="L4" s="8"/>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="3">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3">
+        <v>5</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="C3:C5"/>
+    <mergeCell ref="D3:D5"/>
+    <mergeCell ref="L3:L5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1367,41 +1459,39 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
       </c>
-      <c r="L3" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="L3" s="2"/>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="2"/>
@@ -1412,13 +1502,13 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
   <si>
     <t>编号</t>
   </si>
@@ -150,6 +150,36 @@
     <t>wait</t>
   </si>
   <si>
+    <t>test_2</t>
+  </si>
+  <si>
+    <t>XX1</t>
+  </si>
+  <si>
+    <t>XXX1</t>
+  </si>
+  <si>
+    <t>输入密码</t>
+  </si>
+  <si>
+    <t>//input[@id='passwordA']</t>
+  </si>
+  <si>
+    <t>清空密码</t>
+  </si>
+  <si>
+    <t>clear</t>
+  </si>
+  <si>
+    <t>点击注册按钮</t>
+  </si>
+  <si>
+    <t>click</t>
+  </si>
+  <si>
+    <t>//button</t>
+  </si>
+  <si>
     <t>login_2</t>
   </si>
   <si>
@@ -160,9 +190,6 @@
   </si>
   <si>
     <t>账密正确，登陆成功</t>
-  </si>
-  <si>
-    <t>输入密码</t>
   </si>
 </sst>
 </file>
@@ -838,7 +865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -868,6 +895,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1180,8 +1216,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4"/>
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" style="5" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="5" customWidth="1"/>
@@ -1191,7 +1227,7 @@
     <col min="6" max="6" width="11.625" style="5" customWidth="1"/>
     <col min="7" max="7" width="9.375" style="5" customWidth="1"/>
     <col min="8" max="8" width="10.375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="11.625" style="5" customWidth="1"/>
+    <col min="9" max="9" width="27.125" style="5" customWidth="1"/>
     <col min="10" max="10" width="80.375" style="5" customWidth="1"/>
     <col min="11" max="11" width="11.625" style="5" customWidth="1"/>
     <col min="12" max="16384" width="9" style="5"/>
@@ -1353,13 +1389,230 @@
       <c r="K5" s="3"/>
       <c r="L5" s="9"/>
     </row>
+    <row r="6" s="5" customFormat="1" spans="1:12">
+      <c r="A6" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="3"/>
+      <c r="L6" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" s="5" customFormat="1" spans="1:12">
+      <c r="A7" s="8"/>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="8"/>
+    </row>
+    <row r="8" customFormat="1" spans="1:12">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="3">
+        <v>3</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J8" s="3">
+        <v>123456</v>
+      </c>
+      <c r="K8" s="3"/>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" customFormat="1" spans="1:12">
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="3">
+        <v>4</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3">
+        <v>3</v>
+      </c>
+      <c r="K9" s="3"/>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" customFormat="1" spans="1:12">
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="3">
+        <v>5</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" customFormat="1" spans="1:12">
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="3">
+        <v>6</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" s="3"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3">
+        <v>3</v>
+      </c>
+      <c r="K11" s="3"/>
+      <c r="L11" s="10"/>
+    </row>
+    <row r="12" customFormat="1" spans="1:12">
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="3">
+        <v>7</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="J12" s="3"/>
+      <c r="K12" s="3"/>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="3">
+        <v>8</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3">
+        <v>3</v>
+      </c>
+      <c r="K13" s="3"/>
+      <c r="L13" s="9"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="11"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="10">
     <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A6:A13"/>
     <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B13"/>
     <mergeCell ref="C3:C5"/>
+    <mergeCell ref="C6:C13"/>
     <mergeCell ref="D3:D5"/>
+    <mergeCell ref="D6:D13"/>
     <mergeCell ref="L3:L5"/>
+    <mergeCell ref="L6:L13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1459,16 +1712,16 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
@@ -1502,7 +1755,7 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G4" s="3" t="s">
         <v>32</v>

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="15345" windowHeight="7335"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -865,7 +865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -895,15 +895,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1216,7 +1207,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" style="5" customWidth="1"/>
@@ -1448,10 +1439,10 @@
       <c r="L7" s="8"/>
     </row>
     <row r="8" customFormat="1" spans="1:12">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="3">
         <v>3</v>
       </c>
@@ -1471,13 +1462,13 @@
         <v>123456</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="10"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" customFormat="1" spans="1:12">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="3">
         <v>4</v>
       </c>
@@ -1493,13 +1484,13 @@
         <v>3</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="10"/>
+      <c r="L9" s="8"/>
     </row>
     <row r="10" customFormat="1" spans="1:12">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="3">
         <v>5</v>
       </c>
@@ -1517,13 +1508,13 @@
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
-      <c r="L10" s="10"/>
+      <c r="L10" s="8"/>
     </row>
     <row r="11" customFormat="1" spans="1:12">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="3">
         <v>6</v>
       </c>
@@ -1539,13 +1530,13 @@
         <v>3</v>
       </c>
       <c r="K11" s="3"/>
-      <c r="L11" s="10"/>
+      <c r="L11" s="8"/>
     </row>
     <row r="12" customFormat="1" spans="1:12">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="3">
         <v>7</v>
       </c>
@@ -1563,7 +1554,7 @@
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
-      <c r="L12" s="10"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" spans="1:12">
       <c r="A13" s="9"/>
@@ -1586,20 +1577,6 @@
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="9"/>
-    </row>
-    <row r="14" spans="1:12">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12"/>
-      <c r="J14" s="12"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="15585" windowHeight="7920"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="56">
   <si>
     <t>编号</t>
   </si>
@@ -127,6 +127,18 @@
   </si>
   <si>
     <t>file:///E:/%E6%B5%8B%E8%AF%95/pagetest/pagetest/%E6%B3%A8%E5%86%8CA.html</t>
+  </si>
+  <si>
+    <t>1-1</t>
+  </si>
+  <si>
+    <t>断言url</t>
+  </si>
+  <si>
+    <t>assert_url</t>
+  </si>
+  <si>
+    <t>pagetest</t>
   </si>
   <si>
     <t>输入用户名</t>
@@ -865,7 +877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -888,6 +900,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1207,7 +1225,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="8.375" style="5" customWidth="1"/>
@@ -1337,259 +1355,281 @@
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
-      <c r="E4" s="3">
-        <v>2</v>
+      <c r="E4" s="9" t="s">
+        <v>31</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>35</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="8"/>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="9"/>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
+    <row r="5" s="5" customFormat="1" spans="1:12">
+      <c r="A5" s="10"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
       <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" s="3"/>
+      <c r="L5" s="10"/>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="3">
         <v>3</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3">
-        <v>5</v>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="9"/>
-    </row>
-    <row r="6" s="5" customFormat="1" spans="1:12">
-      <c r="A6" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E6" s="3">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>28</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
-      <c r="J6" s="7" t="s">
-        <v>30</v>
+      <c r="J6" s="3">
+        <v>5</v>
       </c>
       <c r="K6" s="3"/>
-      <c r="L6" s="6" t="b">
-        <v>1</v>
-      </c>
+      <c r="L6" s="11"/>
     </row>
     <row r="7" s="5" customFormat="1" spans="1:12">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>44</v>
+      </c>
       <c r="E7" s="3">
+        <v>1</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" s="3"/>
+      <c r="I7" s="3"/>
+      <c r="J7" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="3"/>
+      <c r="L7" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" s="5" customFormat="1" spans="1:12">
+      <c r="A8" s="10"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="3">
         <v>2</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="F8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="8"/>
-    </row>
-    <row r="8" customFormat="1" spans="1:12">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="3">
-        <v>3</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J8" s="3">
-        <v>123456</v>
+        <v>38</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>39</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="8"/>
+      <c r="L8" s="10"/>
     </row>
     <row r="9" customFormat="1" spans="1:12">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="A9" s="10"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
       <c r="E9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F9" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="H9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+      <c r="I9" s="3" t="s">
+        <v>46</v>
+      </c>
       <c r="J9" s="3">
-        <v>3</v>
+        <v>123456</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="8"/>
+      <c r="L9" s="10"/>
     </row>
     <row r="10" customFormat="1" spans="1:12">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="10"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
       <c r="E10" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="J10" s="3"/>
+        <v>41</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3">
+        <v>3</v>
+      </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="8"/>
+      <c r="L10" s="10"/>
     </row>
     <row r="11" customFormat="1" spans="1:12">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="A11" s="10"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
       <c r="E11" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3">
-        <v>3</v>
-      </c>
+      <c r="I11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="8"/>
+      <c r="L11" s="10"/>
     </row>
     <row r="12" customFormat="1" spans="1:12">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
       <c r="E12" s="3">
+        <v>6</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3">
+        <v>3</v>
+      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" customFormat="1" spans="1:12">
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="3">
         <v>7</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="8"/>
+      <c r="F13" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="10"/>
     </row>
-    <row r="13" spans="1:12">
-      <c r="A13" s="9"/>
-      <c r="B13" s="9"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="3">
+    <row r="14" spans="1:12">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="3">
         <v>8</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3">
+      <c r="F14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
         <v>3</v>
       </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="9"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="A6:A13"/>
-    <mergeCell ref="B3:B5"/>
-    <mergeCell ref="B6:B13"/>
-    <mergeCell ref="C3:C5"/>
-    <mergeCell ref="C6:C13"/>
-    <mergeCell ref="D3:D5"/>
-    <mergeCell ref="D6:D13"/>
-    <mergeCell ref="L3:L5"/>
-    <mergeCell ref="L6:L13"/>
+    <mergeCell ref="A3:A6"/>
+    <mergeCell ref="A7:A14"/>
+    <mergeCell ref="B3:B6"/>
+    <mergeCell ref="B7:B14"/>
+    <mergeCell ref="C3:C6"/>
+    <mergeCell ref="C7:C14"/>
+    <mergeCell ref="D3:D6"/>
+    <mergeCell ref="D7:D14"/>
+    <mergeCell ref="L3:L6"/>
+    <mergeCell ref="L7:L14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1689,34 +1729,34 @@
     </row>
     <row r="3" spans="1:12">
       <c r="A3" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E3" s="3">
         <v>1</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K3" s="3">
         <v>0</v>
@@ -1732,13 +1772,13 @@
         <v>2</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I4" s="3"/>
       <c r="J4" s="3">

--- a/data/测试用例.xlsx
+++ b/data/测试用例.xlsx
@@ -877,7 +877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -907,9 +907,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1234,7 +1231,7 @@
     <col min="4" max="4" width="19.125" style="5" customWidth="1"/>
     <col min="5" max="5" width="10.375" style="5" customWidth="1"/>
     <col min="6" max="6" width="11.625" style="5" customWidth="1"/>
-    <col min="7" max="7" width="9.375" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="5" customWidth="1"/>
     <col min="8" max="8" width="10.375" style="5" customWidth="1"/>
     <col min="9" max="9" width="27.125" style="5" customWidth="1"/>
     <col min="10" max="10" width="80.375" style="5" customWidth="1"/>
@@ -1373,10 +1370,10 @@
       <c r="L4" s="8"/>
     </row>
     <row r="5" s="5" customFormat="1" spans="1:12">
-      <c r="A5" s="10"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
+      <c r="A5" s="8"/>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8"/>
       <c r="E5" s="3">
         <v>2</v>
       </c>
@@ -1396,13 +1393,13 @@
         <v>39</v>
       </c>
       <c r="K5" s="3"/>
-      <c r="L5" s="10"/>
+      <c r="L5" s="8"/>
     </row>
     <row r="6" spans="1:12">
-      <c r="A6" s="11"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
+      <c r="A6" s="10"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
       <c r="E6" s="3">
         <v>3</v>
       </c>
@@ -1418,7 +1415,7 @@
         <v>5</v>
       </c>
       <c r="K6" s="3"/>
-      <c r="L6" s="11"/>
+      <c r="L6" s="10"/>
     </row>
     <row r="7" s="5" customFormat="1" spans="1:12">
       <c r="A7" s="6" t="s">
@@ -1453,10 +1450,10 @@
       </c>
     </row>
     <row r="8" s="5" customFormat="1" spans="1:12">
-      <c r="A8" s="10"/>
-      <c r="B8" s="10"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="A8" s="8"/>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8"/>
       <c r="E8" s="3">
         <v>2</v>
       </c>
@@ -1476,13 +1473,13 @@
         <v>39</v>
       </c>
       <c r="K8" s="3"/>
-      <c r="L8" s="10"/>
+      <c r="L8" s="8"/>
     </row>
     <row r="9" customFormat="1" spans="1:12">
-      <c r="A9" s="10"/>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8"/>
       <c r="E9" s="3">
         <v>3</v>
       </c>
@@ -1502,13 +1499,13 @@
         <v>123456</v>
       </c>
       <c r="K9" s="3"/>
-      <c r="L9" s="10"/>
+      <c r="L9" s="8"/>
     </row>
     <row r="10" customFormat="1" spans="1:12">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
       <c r="E10" s="3">
         <v>4</v>
       </c>
@@ -1524,13 +1521,13 @@
         <v>3</v>
       </c>
       <c r="K10" s="3"/>
-      <c r="L10" s="10"/>
+      <c r="L10" s="8"/>
     </row>
     <row r="11" customFormat="1" spans="1:12">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10"/>
+      <c r="A11" s="8"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
       <c r="E11" s="3">
         <v>5</v>
       </c>
@@ -1548,13 +1545,13 @@
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
-      <c r="L11" s="10"/>
+      <c r="L11" s="8"/>
     </row>
     <row r="12" customFormat="1" spans="1:12">
-      <c r="A12" s="10"/>
-      <c r="B12" s="10"/>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
+      <c r="A12" s="8"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
       <c r="E12" s="3">
         <v>6</v>
       </c>
@@ -1570,13 +1567,13 @@
         <v>3</v>
       </c>
       <c r="K12" s="3"/>
-      <c r="L12" s="10"/>
+      <c r="L12" s="8"/>
     </row>
     <row r="13" customFormat="1" spans="1:12">
-      <c r="A13" s="10"/>
-      <c r="B13" s="10"/>
-      <c r="C13" s="10"/>
-      <c r="D13" s="10"/>
+      <c r="A13" s="8"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
       <c r="E13" s="3">
         <v>7</v>
       </c>
@@ -1594,13 +1591,13 @@
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="10"/>
+      <c r="L13" s="8"/>
     </row>
     <row r="14" spans="1:12">
-      <c r="A14" s="11"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
+      <c r="A14" s="10"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
       <c r="E14" s="3">
         <v>8</v>
       </c>
@@ -1616,7 +1613,7 @@
         <v>3</v>
       </c>
       <c r="K14" s="3"/>
-      <c r="L14" s="11"/>
+      <c r="L14" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="10">
